--- a/Zinc/5. Statistical data analysis/Plots by typology/Probability_of_toxicity.xlsx
+++ b/Zinc/5. Statistical data analysis/Plots by typology/Probability_of_toxicity.xlsx
@@ -20,13 +20,13 @@
     <t xml:space="preserve">Overlap_Daphnia</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Tributaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tributaries</t>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Developed Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>

--- a/Zinc/5. Statistical data analysis/Plots by typology/Probability_of_toxicity.xlsx
+++ b/Zinc/5. Statistical data analysis/Plots by typology/Probability_of_toxicity.xlsx
@@ -20,13 +20,13 @@
     <t xml:space="preserve">Overlap_Daphnia</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Developed Tribs</t>
+    <t xml:space="preserve">NP Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">Main Stem</t>
